--- a/class_diagram/controller/manager/成績管理sys_クラス図_controller_manager.xlsx
+++ b/class_diagram/controller/manager/成績管理sys_クラス図_controller_manager.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="304" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECDCA860-A728-4C0A-80F8-7287F513A714}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0F40657-8BBE-46BC-B8B6-02981BAABF6C}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="12" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MajorsSearchGetController" sheetId="8" r:id="rId1"/>
-    <sheet name="MajorsGetController" sheetId="3" r:id="rId2"/>
-    <sheet name="MajorRegisterController" sheetId="2" r:id="rId3"/>
-    <sheet name="MajorSetController" sheetId="6" r:id="rId4"/>
-    <sheet name="MajorDeleteController" sheetId="7" r:id="rId5"/>
-    <sheet name="LoginController" sheetId="9" r:id="rId6"/>
+    <sheet name="LoginController" sheetId="9" r:id="rId1"/>
+    <sheet name="MajorsSearchGetController" sheetId="8" r:id="rId2"/>
+    <sheet name="MajorsGetController" sheetId="3" r:id="rId3"/>
+    <sheet name="MajorRegisterController" sheetId="2" r:id="rId4"/>
+    <sheet name="MajorSetController" sheetId="6" r:id="rId5"/>
+    <sheet name="MajorDeleteController" sheetId="7" r:id="rId6"/>
     <sheet name="MajorGetController" sheetId="4" r:id="rId7"/>
     <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId8"/>
+    <sheet name="SubjectsGetController" sheetId="10" r:id="rId9"/>
+    <sheet name="SubjectGetController" sheetId="11" r:id="rId10"/>
+    <sheet name="SubjectDeleteController" sheetId="12" r:id="rId11"/>
+    <sheet name="SubjectSetController" sheetId="13" r:id="rId12"/>
+    <sheet name="SubjectRegisterController" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -92,6 +97,2276 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5E257E0-DC21-4CD6-80BF-BAC139C0C8CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>LoginController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B1865E6-6D20-407A-8053-4F6E75FBC50A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B5E257E0-DC21-4CD6-80BF-BAC139C0C8CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="2105025"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : ManagerService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0548C456-7320-4F3D-9F2B-1DF1CDED8122}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2B1865E6-6D20-407A-8053-4F6E75FBC50A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@PostMapping("/manager/login")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>login( session : HttpSession, redirectAttributes RedirectAttributes, form LoginForm)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9427D7D0-F6BB-442B-B466-23F99AB59FC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectDeleteController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F30C4AE8-C68E-48C2-B696-B3FB6CA97A22}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9427D7D0-F6BB-442B-B466-23F99AB59FC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="2105025"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : SubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8972238-AB01-4427-B0AC-2A1CE78010EC}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F30C4AE8-C68E-48C2-B696-B3FB6CA97A22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/subject_delete")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>deleteSubject( session : HttpSession, id : @RequestParam int )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DFE20A2-AB4D-4EB8-BDA0-C028EA33B73C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectSetController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C870B746-E91C-454E-8296-A322450E1C04}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1DFE20A2-AB4D-4EB8-BDA0-C028EA33B73C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="2105025"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : SubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63773C6B-94BD-4661-B6B6-67BBE4CF1BBA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C870B746-E91C-454E-8296-A322450E1C04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/subject_update")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getSubject( session : HttpSession, redirectAttributes RedirectAttributes, id : @RequestParam int )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FED257F1-690C-4CA7-94A4-1D0FC988B319}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{63773C6B-94BD-4661-B6B6-67BBE4CF1BBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1095375" y="4086225"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@PostMapping("/manager/subject_update")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>setSubject( session : HttpSession, form : SubjectSetForm)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30F533DC-CF51-40DE-9AF5-3121DDFB11D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectRegisterController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40F3AB43-3A2D-4E9F-A10C-780F61487CF8}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{30F533DC-CF51-40DE-9AF5-3121DDFB11D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1123950" y="3848100"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@PostMapping("/manager/subject_register")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>registerSubject( session : HttpSession, form : SubjectRegisterForm)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF040D5A-A94C-4C4B-82E6-9A77C890EF9F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{40F3AB43-3A2D-4E9F-A10C-780F61487CF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1152525" y="2057400"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : SubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
@@ -537,7 +2812,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -987,7 +3262,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1245,7 +3520,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>registerMajor( session : HttpSession, redirectAttributes RedirectAttributes, form : MajorRegisterForm)</a:t>
+            <a:t>registerMajor( session : HttpSession,  form : MajorRegisterForm)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1437,7 +3712,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2153,7 +4428,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>setMajor( session : HttpSession, form : MajorSetForm, id : @RequestParam int )</a:t>
+            <a:t>setMajor( session : HttpSession, form : MajorSetForm)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2175,7 +4450,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2695,547 +4970,6 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>deleteMajor( session : HttpSession, id : @RequestParam int )</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>-r String</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="角丸四角形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5E257E0-DC21-4CD6-80BF-BAC139C0C8CC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="695325" y="914400"/>
-          <a:ext cx="12677775" cy="5495925"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="90000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle>
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>LoginController</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="四角形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B1865E6-6D20-407A-8053-4F6E75FBC50A}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B5E257E0-DC21-4CD6-80BF-BAC139C0C8CC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1085850" y="2105025"/>
-          <a:ext cx="2733675" cy="352425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
-            <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle>
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>service : ManagerService</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="四角形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0548C456-7320-4F3D-9F2B-1DF1CDED8122}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2B1865E6-6D20-407A-8053-4F6E75FBC50A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1085850" y="3028950"/>
-          <a:ext cx="9020175" cy="876300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
-            <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle>
-          <a:lvl1pPr marL="0" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" indent="0">
-            <a:defRPr sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>@PostMapping("/manager/login")</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>login( session : HttpSession, redirectAttributes RedirectAttributes, form LoginForm)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3777,6 +5511,997 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>getMajor( session : HttpSession, redirectAttributes RedirectAttributes,  id : @RequestParam int )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BAB37BB-A8D9-483C-B909-8154C4A92D07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectsGetController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55F4A9D4-FC18-4090-8355-8E81835E43B1}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8BAB37BB-A8D9-483C-B909-8154C4A92D07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1238250" y="3962400"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/subjects")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getSubjects( session : HttpSession, redirectAttributes RedirectAttributes)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5B58179-931D-44E2-A0C2-3B191A3F0249}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{55F4A9D4-FC18-4090-8355-8E81835E43B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1133475" y="2457450"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : SubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6672FEE1-95FF-468E-8A36-D852DC2DC12D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>SubjectGetController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0114744B-1DF3-46B6-A7CE-29FD9C8CC485}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6672FEE1-95FF-468E-8A36-D852DC2DC12D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="2105025"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : SubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ABCA90D-C662-45B4-8364-0D8A28F3AB2F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0114744B-1DF3-46B6-A7CE-29FD9C8CC485}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/subject")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getSubject( session : HttpSession, redirectAttributes RedirectAttributes,  id : @RequestParam int )</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4114,6 +6839,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1C81B42-A39D-498F-89CA-4A546B1B72A5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51B6A9DA-23D8-4E9C-BBA7-D0E31A41B974}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47344553-384A-4AE6-B86F-DB49F0E5832C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21D7C824-6AEF-4247-A507-2832CA8C0ED4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B01745C-A106-479F-A875-A0E39E2B91CC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{114528CA-A902-433C-AF18-803E54EF3AD4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -4123,7 +6898,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FAD6FA3-7B26-471B-B3D8-8BC601EF4900}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -4133,7 +6908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A8633E-387F-40CD-BD90-4057C77280B7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -4143,7 +6918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8829FDBE-9BFC-4C0E-89F2-C13862F39AFB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -4153,18 +6928,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A33E3BB5-DA31-4079-B9F6-134463708F63}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1C81B42-A39D-498F-89CA-4A546B1B72A5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData/>
@@ -4190,4 +6955,14 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0395B2B9-B527-46F5-91DB-5CBA00DB0223}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/class_diagram/controller/manager/成績管理sys_クラス図_controller_manager.xlsx
+++ b/class_diagram/controller/manager/成績管理sys_クラス図_controller_manager.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="349" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0F40657-8BBE-46BC-B8B6-02981BAABF6C}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6B92E5D-81F2-43C0-8215-8F53BFAEE823}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="12" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginController" sheetId="9" r:id="rId1"/>
@@ -21,6 +21,11 @@
     <sheet name="SubjectDeleteController" sheetId="12" r:id="rId11"/>
     <sheet name="SubjectSetController" sheetId="13" r:id="rId12"/>
     <sheet name="SubjectRegisterController" sheetId="14" r:id="rId13"/>
+    <sheet name="ClassSetController" sheetId="15" r:id="rId14"/>
+    <sheet name="ClassRegisterController" sheetId="16" r:id="rId15"/>
+    <sheet name="ClassDeleteController" sheetId="17" r:id="rId16"/>
+    <sheet name="ClassGetController" sheetId="18" r:id="rId17"/>
+    <sheet name="ClassesGetController" sheetId="19" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -2353,6 +2358,2726 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>service : SubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29C10924-D337-468B-BC74-7A2FE8857E78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassSetController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A5D9AD4-2756-448D-B493-FB005050B438}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{29C10924-D337-468B-BC74-7A2FE8857E78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="2105025"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : ClassService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DE416BD-E087-435B-8DBB-EC59526C24D4}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9A5D9AD4-2756-448D-B493-FB005050B438}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/class_update")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getClass( session : HttpSession, redirectAttributes RedirectAttributes, id : @RequestParam int )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F752916A-1326-4D70-AC8D-03BACE1FC3B8}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2DE416BD-E087-435B-8DBB-EC59526C24D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1095375" y="4086225"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@PostMapping("/manager/class_update")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>setClass( session : HttpSession, form : ClassSetForm)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C1BE9ED-5637-4887-AE64-1977B8D6BB94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassRegisterController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F793176-1180-491C-A2B2-9DF49DD3BABF}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4C1BE9ED-5637-4887-AE64-1977B8D6BB94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1123950" y="3848100"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@PostMapping("/manager/class_register")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>registerClass( session : HttpSession, form : ClassRegisterForm)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{558D8355-0B75-435F-AB14-5ED253931484}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9F793176-1180-491C-A2B2-9DF49DD3BABF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1152525" y="2057400"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : ClassService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0C508EF-58BA-48D9-B1EB-A6A1367283A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassDeleteController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{530B0F91-2F62-4474-8035-A346B65E7942}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F0C508EF-58BA-48D9-B1EB-A6A1367283A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="2105025"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : ClassService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BB5BFD6-FE5A-466C-8F1A-13BBB3BF3633}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{530B0F91-2F62-4474-8035-A346B65E7942}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/class_delete")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>deleteClass( session : HttpSession, id : @RequestParam int )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02E92648-E0AF-4C3B-B0E4-678D1C5F86FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassGetController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D25468F5-76DE-4C1F-9018-A988E0D7CB9A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{02E92648-E0AF-4C3B-B0E4-678D1C5F86FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="2105025"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : ClassService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB5A1021-2B08-4E88-8417-B85BD9D78219}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D25468F5-76DE-4C1F-9018-A988E0D7CB9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/class")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getClass( session : HttpSession, redirectAttributes RedirectAttributes,  id : @RequestParam int )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDD032F9-352D-43A7-8057-96070C8CD968}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1028700"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassesGetController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E33295CC-650C-4E20-96DF-EBD3054E63C7}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{CDD032F9-352D-43A7-8057-96070C8CD968}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1190625" y="4038600"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/classes")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getClasses( session : HttpSession, redirectAttributes RedirectAttributes)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F90A1C1F-5048-4101-92DF-F92D0C26DC83}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E33295CC-650C-4E20-96DF-EBD3054E63C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1133475" y="2457450"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : ClassService</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6888,6 +9613,56 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3703342A-FD22-4B6D-A604-1BAF72F4C733}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F608E806-1F75-4B70-8234-708FE8C247BA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6337DC-4FF5-4552-918F-0200BAEA4FD5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40FF84C0-0B37-4112-B1C5-792A169FB4B8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A358B4D7-1C56-4751-9632-CD10F06CF323}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{114528CA-A902-433C-AF18-803E54EF3AD4}">
   <dimension ref="A1"/>

--- a/class_diagram/controller/manager/成績管理sys_クラス図_controller_manager.xlsx
+++ b/class_diagram/controller/manager/成績管理sys_クラス図_controller_manager.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="388" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6B92E5D-81F2-43C0-8215-8F53BFAEE823}"/>
+  <xr:revisionPtr revIDLastSave="393" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0377A3F8-38AA-418C-91A1-51BF0A245075}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="17" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginController" sheetId="9" r:id="rId1"/>
@@ -24,8 +24,9 @@
     <sheet name="ClassSetController" sheetId="15" r:id="rId14"/>
     <sheet name="ClassRegisterController" sheetId="16" r:id="rId15"/>
     <sheet name="ClassDeleteController" sheetId="17" r:id="rId16"/>
-    <sheet name="ClassGetController" sheetId="18" r:id="rId17"/>
-    <sheet name="ClassesGetController" sheetId="19" r:id="rId18"/>
+    <sheet name="ManagerGetController" sheetId="20" r:id="rId17"/>
+    <sheet name="ClassGetController" sheetId="18" r:id="rId18"/>
+    <sheet name="ClassesGetController" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -4116,6 +4117,557 @@
         <xdr:cNvPr id="2" name="角丸四角形 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E17A48BD-C8B0-44BB-B6E5-075D192951D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="914400"/>
+          <a:ext cx="12677775" cy="5495925"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ManagerGetController</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DE7D7E8-E7FA-4718-AF48-1479A34B5AA4}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E17A48BD-C8B0-44BB-B6E5-075D192951D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="2105025"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>service : ManagerService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3DF0A51-073F-43E9-832B-DB4BACBB6445}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6DE7D7E8-E7FA-4718-AF48-1479A34B5AA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1085850" y="3028950"/>
+          <a:ext cx="9020175" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>@GetMapping("/manager/manager_get")</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getManager( session : HttpSession, redirectAttributes RedirectAttributes )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02E92648-E0AF-4C3B-B0E4-678D1C5F86FD}"/>
             </a:ext>
           </a:extLst>
@@ -4637,7 +5189,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -9644,6 +10196,16 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B58121-50DE-43FD-8B23-A116E15A5343}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40FF84C0-0B37-4112-B1C5-792A169FB4B8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -9653,7 +10215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A358B4D7-1C56-4751-9632-CD10F06CF323}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>

--- a/class_diagram/controller/manager/成績管理sys_クラス図_controller_manager.xlsx
+++ b/class_diagram/controller/manager/成績管理sys_クラス図_controller_manager.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="393" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0377A3F8-38AA-418C-91A1-51BF0A245075}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB613E71-8609-4462-9C6F-76532D8F3964}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="17" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="16" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginController" sheetId="9" r:id="rId1"/>
@@ -3553,6 +3553,516 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ED5038E-F78B-4A04-BA4C-32834CDB4B76}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{558D8355-0B75-435F-AB14-5ED253931484}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4248150" y="2047875"/>
+          <a:ext cx="2733675" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectService : SubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD481C17-132C-441F-878C-A4A8029DC4A7}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1ED5038E-F78B-4A04-BA4C-32834CDB4B76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7191375" y="2047875"/>
+          <a:ext cx="3076575" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>managerService : ManagerService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B39458BC-E3FF-41F7-B92C-216BDD07B810}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{CD481C17-132C-441F-878C-A4A8029DC4A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1143000" y="2619375"/>
+          <a:ext cx="5076825" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>classSubjectService : ClassSubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5180,6 +5690,176 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>-r String</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{822D74BA-3C0F-4A1F-B8B6-290C836A5719}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EB5A1021-2B08-4E88-8417-B85BD9D78219}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3933825" y="2105025"/>
+          <a:ext cx="5362575" cy="352425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>classSubjectService : ClassSubjectService</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
